--- a/public/business-plans/tourism.xlsx
+++ b/public/business-plans/tourism.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Туризм и индустрия гостеприимства». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Туризм и индустрия гостеприимства». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,31 +604,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Гостевой дом «Ipak Yoli Inn» на 8 номеров открывается в историческом центре Бухары с фокусом на индивидуальных туристов из Европы и Юго-Восточной Азии. Требуемые инвестиции — 950 млн сум на ремонт исторического здания и меблировку; окупаемость — около 3 сезонов при средней загрузке 55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -628,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -641,70 +661,94 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="59" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>•  Узбекистан активно развивает въездной туризм: упрощён визовый режим для многих стран, растёт число иностранных туристов к историческим городам (Самарканд, Бухара, Хива).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>•  Узбекистан переживает бум въездного туризма: по данным UzDaily и Nuz.uz, за январь–июль 2026 года страну посетили 7,74 млн иностранных туристов — рост на 22,6% год к году, а экспорт туристических услуг за тот же период достиг $3,895 млрд (+56% год к году) (nuz.uz, uzdaily.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="59" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>•  Действует упрощённое лицензирование малых средств размещения и меры поддержки туристического бизнеса.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>•  Узбекистан входит в топ-5 стран мира по темпам роста туристического потока (yuz.uz) — это открывает окно возможностей, но одновременно означает быстрый приток новых игроков и рост конкуренции за туристов и кадры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>•  Растёт спрос на нишевые форматы: гастрономический, паломнический и эко-туризм.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>•  Инфраструктура размещения растёт вслед за спросом: только за первые 7 месяцев 2026 года появилось 705 новых объектов размещения (nuz.uz) — рынок мини-отелей и гостевых домов активно насыщается, особенно в Самарканде, Бухаре и Хиве.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>•  [Впишите] Сезонность и загрузку в вашем регионе, средний чек конкурентов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+          <t>•  Действует упрощённое лицензирование малых средств размещения и меры поддержки туристического бизнеса; для многих направлений (Россия, страны СНГ, ряд государств Азии) действует упрощённый или безвизовый режим въезда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Растёт спрос на нишевые форматы: гастрономический, паломнический и эко-туризм, а также культурно-исторический туризм вне «золотого треугольника» Самарканд-Бухара-Хива — менее насыщенные регионы дают больше пространства для нового бизнеса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: Казахстан делает ставку на природный и деловой туризм (Алматы, Астана), а не на культурно-исторический — Узбекистан по историческому наследию Шёлкового пути конкурентов в регионе практически не имеет, но уступает соседям в развитости туристической инфраструктуры вне основных городов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Сезонность и загрузку в вашем регионе, средний чек конкурентов — уточняйте по данным Госкомтуризма (uzbekistan.travel) и локальным ассоциациям гостиниц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Конкуренты</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Целевая аудитория</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -716,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -729,117 +773,183 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цена — на уровне среднего чека по Бухаре с наценкой за аутентичный дизайн и завтрак из местной кухни; продвижение — листинг на Booking.com и Airbnb с профессиональными фото, партнёрство с местными гидами и туроператорами, работа с отзывами для рейтинга площадок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: бронирование через платформы или напрямую → заселение → обслуживание в течение проживания (завтрак, уборка, консьерж-услуги) → выезд и сбор отзыва. Требуется регистрация и сертификация средства размещения, санитарные разрешения для точки питания при её наличии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Управляющий-владелец, администратор ресепшена (посменно), 2 горничные, повар для завтраков на part-time. Форма — ИП или ООО в зависимости от масштаба и планов расширения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Сезонность спроса</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Гибкое ценообразование, доп. услуги в межсезонье</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Высокие комиссии онлайн-платформ</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Развитие прямых каналов продаж и повторных бронирований</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Изменение визовых/пограничных правил</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Мониторинг регуляторики въездного туризма</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="13" ht="59" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Сезонность спроса (спад в жаркие летние и зимние месяцы)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Гибкое ценообразование, дополнительные услуги и пакеты в межсезонье, работа с внутренним туризмом</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Высокие комиссии онлайн-платформ бронирования</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Развитие прямых каналов продаж, программа повторных бронирований и постоянных клиентов</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Изменение визовых/пограничных правил для ключевых рынков</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Мониторинг регуляторики въездного туризма, диверсификация географии привлекаемых туристов</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Быстрый рост числа новых объектов размещения и обострение конкуренции</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Чёткое позиционирование и УТП (ниша, дизайн, сервис), а не конкуренция только по цене</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Дефицит квалифицированного гостиничного персонала (особенно со знанием языков)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Обучение персонала, конкурентные условия труда, частичная автоматизация ресепшена</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="59" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ущерб историческим объектам/инфраструктуре от резкого роста турпотока</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Учёт норм охраны исторического наследия при ремонте, участие в программах устойчивого туризма</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,329 +961,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Ремонт/обустройство помещения под номерной фонд</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>особенно важно для исторических зданий</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Мебель и оборудование</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Регистрация и сертификация гостиницы</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Продвижение на туристических платформах</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Booking.com, Airbnb и др.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Профессиональная фотосъёмка объекта</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>критично для конверсии на платформах бронирования</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Лицензии на доп. услуги</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>питание, экскурсии — при необходимости</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B12" s="15">
-        <f>SUM(B7:B11)</f>
+      <c r="B13" s="16">
+        <f>SUM(B7:B12)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="C13" s="17" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Проживание</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>посуточно / по бронированиям</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Дополнительные услуги</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>питание, экскурсии, трансфер</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Корпоративные и групповые туры</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>SUM(B15:B17)</f>
+      <c r="B19" s="16">
+        <f>SUM(B16:B18)</f>
         <v/>
       </c>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C19" s="17" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>ФОТ персонала</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Комиссии платформ бронирования</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Закупки для питания/уборки</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Маркетинг и реклама</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>включая продвижение на Booking.com/Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B26" s="15">
-        <f>SUM(B21:B25)</f>
+      <c r="B27" s="16">
+        <f>SUM(B22:B26)</f>
         <v/>
       </c>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="C27" s="17" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Ежемесячная прибыль</t>
         </is>
       </c>
-      <c r="B28" s="10">
-        <f>B18-B26</f>
+      <c r="B29" s="11">
+        <f>B19-B27</f>
         <v/>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B30" s="13">
-        <f>IFERROR(B4/B28,"—")</f>
+      <c r="B31" s="14">
+        <f>IFERROR(B4/B29,"—")</f>
         <v/>
       </c>
-      <c r="C30" s="13">
+      <c r="C31" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B31" s="17">
-        <f>IFERROR(B28/B18*100,"—")</f>
+      <c r="B32" s="18">
+        <f>IFERROR(B29/B19*100,"—")</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C32" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="33"/>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/business-plans/tourism.xlsx
+++ b/public/business-plans/tourism.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: ТУРИЗМ И ИНДУСТРИЯ ГОСТЕПРИИМСТВА</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: ТУРИЗМ И ИНДУСТРИЯ ГОСТЕПРИИМСТВА — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Туризм и индустрия гостеприимства» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Туризм и индустрия гостеприимства» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B16</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,85 +563,93 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Ремонт/обустройство помещения под номерной фонд</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
+        <v>620000000</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>особенно важно для исторических зданий</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+          <t>особенно важно для исторических зданий — Пример: реставрация историч. здания под 8 номеров с санузлами и двориком в центре Бухары, ~77,5 млн сум/номер — оценка по типовым сметам реставрации</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Мебель и оборудование</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+        <v>240000000</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Пример: мебель нац. стиля, кондиционеры, бельё, кухня и лобби — ~30 млн сум/номер, оценка по рыночным ценам</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Регистрация и сертификация гостиницы</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+        <v>20000000</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: регистрация, сертификация средства размещения, пожарные/санитарные разрешения</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Продвижение на туристических платформах</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>30000000</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Booking.com, Airbnb и др.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+          <t>Booking.com, Airbnb и др. — Пример: оценка: подключение Booking.com/Airbnb/Ostrovok, channel manager, стартовые платные размещения</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Профессиональная фотосъёмка объекта</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>критично для конверсии на платформах бронирования</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+          <t>критично для конверсии на платформах бронирования — Пример: оценка по рыночным расценкам фотографов в Бухаре/Ташкенте</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Лицензии на доп. услуги</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>питание, экскурсии — при необходимости</t>
+          <t>питание, экскурсии — при необходимости — Пример: оценка: разрешение на общепит (завтраки), договоры с туроператорами/гидами</t>
         </is>
       </c>
     </row>
@@ -659,46 +675,50 @@
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
     </row>
-    <row r="19" ht="21" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Проживание</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
+        <v>63000000</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>посуточно / по бронированиям</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+          <t>посуточно / по бронированиям — Пример: 8 номеров × 30 дн × загрузка 55% = 132 номера-ночи/мес × ~480 тыс. сум/ночь (~38$) — в диапазоне цен гостевых домов Бухары 19-60+$/ночь (kayak.com, hotels.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Дополнительные услуги</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>питание, экскурсии, трансфер</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
+          <t>питание, экскурсии, трансфер — Пример: ~16% от выручки за проживание — завтраки, трансферы, прачечная, экскурсии, типично для формата B&amp;B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Корпоративные и групповые туры</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
+        <v>7000000</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: договорные блок-брони с турагентствами, усреднено помесячно с учётом сезонности</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -722,62 +742,78 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
     </row>
-    <row r="25" ht="21" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ФОТ персонала</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26" ht="21" customHeight="1">
+        <v>23000000</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Пример: управляющий, 2 администратора-горничные, повар, уборщица, охранник (~6 чел.); ориентир — средняя зарплата по Узбекистану 6,16 млн / Ташкенту 10,38 млн сум (Госкомстат/gazeta.uz, окт. 2025), скорректировано на регион Бухары</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <v>7500000</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка по среднему тарифу для малых гостиниц на 8 номеров</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Комиссии платформ бронирования</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>5700000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~15% комиссия Booking.com/Ostrovok с ~60% броней через OTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Закупки для питания/уборки</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
+        <v>9000000</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: продукты для завтраков, моющие средства, бельё в прачечную</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="51" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Маркетинг и реклама</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>включая продвижение на Booking.com/Airbnb</t>
+          <t>включая продвижение на Booking.com/Airbnb — Пример: оценка: локальная реклама, соцсети, работа с блогерами/турагентствами</t>
         </is>
       </c>
     </row>
@@ -816,9 +852,10 @@
         <f>IFERROR(B7/B32,"—")</f>
         <v/>
       </c>
-      <c r="C34" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -831,24 +868,34 @@
         <f>IFERROR(B32/B22*100,"—")</f>
         <v/>
       </c>
-      <c r="C35" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="36"/>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="37" ht="50" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: Сумма стартовых затрат — 940 млн сум (≈99% от заявленных 950 млн). Прибыль ≈29,8 млн сум/мес даёт окупаемость ≈31,5 мес. — соответствует заявленным ~3 сезонам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39" ht="55" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
